--- a/task_submission/4.1 内存自验证报告.xlsx
+++ b/task_submission/4.1 内存自验证报告.xlsx
@@ -760,6 +760,38 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="11430000" cy="7143750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="1f783e22-e195-4794-bef1-1ea5acf1e0bf"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R29a4323713094529"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -1005,14 +1037,16 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" customHeight="1">
-      <x:c r="A1" s="13" t="str">
-        <x:v>内存测试总结：PyTorch NPU 活跃张量分配增量，开发环境自测
+      <x:c r="A1" s="13" t="inlineStr">
+        <x:is>
+          <x:t>内存测试总结：PyTorch NPU 活跃张量分配增量，开发环境自测
 1、Ascend910_9382 / CANN 9.1.0；指定 OS/驱动待复测。
 2、计划 35，适用 10，实测通过 10，失败 0，未测 0；其余 25 不适用（任务书 3.5）。
 3、显式 workspace=0；allocated/active 峰值增量均≤输出字节+16 KiB，释放回基线。
 4、F 为 active 峰值增量/10^9，单位 GB；不是整卡 HBM；标杆未测，rato 不可计算。
 5、20 次重复回收仅 018 的两入口实测；2×64 KiB 片上 UB 不计入张量分配。
-6、shape=[B,H,L,D]；完整字节数/回收记录见“完整统计”；截图待补。</x:v>
+6、shape=[B,H,L,D]；完整字节数/回收记录见“完整统计”；真实截图见D40（本次补测）。</x:t>
+        </x:is>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1094,8 +1128,10 @@
       <x:c r="C5" s="17" t="str">
         <x:v>通过</x:v>
       </x:c>
-      <x:c r="D5" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
+      <x:c r="D5" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
       </x:c>
       <x:c r="E5" t="str" s="19">
         <x:v>未测</x:v>
@@ -1199,8 +1235,10 @@
       <x:c r="C9" s="17" t="str">
         <x:v>通过</x:v>
       </x:c>
-      <x:c r="D9" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
+      <x:c r="D9" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
       </x:c>
       <x:c r="E9" t="str" s="19">
         <x:v>未测</x:v>
@@ -1226,8 +1264,10 @@
       <x:c r="C10" s="17" t="str">
         <x:v>通过</x:v>
       </x:c>
-      <x:c r="D10" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
+      <x:c r="D10" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
       </x:c>
       <x:c r="E10" t="str" s="19">
         <x:v>未测</x:v>
@@ -1253,8 +1293,10 @@
       <x:c r="C11" s="17" t="str">
         <x:v>通过</x:v>
       </x:c>
-      <x:c r="D11" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
+      <x:c r="D11" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
       </x:c>
       <x:c r="E11" t="str" s="19">
         <x:v>未测</x:v>
@@ -1280,8 +1322,10 @@
       <x:c r="C12" s="17" t="str">
         <x:v>通过</x:v>
       </x:c>
-      <x:c r="D12" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
+      <x:c r="D12" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
       </x:c>
       <x:c r="E12" t="str" s="19">
         <x:v>未测</x:v>
@@ -1359,8 +1403,10 @@
       <x:c r="C15" s="17" t="str">
         <x:v>通过</x:v>
       </x:c>
-      <x:c r="D15" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
+      <x:c r="D15" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
       </x:c>
       <x:c r="E15" t="str" s="15">
         <x:v>未测</x:v>
@@ -1464,8 +1510,10 @@
       <x:c r="C19" s="17" t="str">
         <x:v>通过</x:v>
       </x:c>
-      <x:c r="D19" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
+      <x:c r="D19" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
       </x:c>
       <x:c r="E19" t="str" s="15">
         <x:v>未测</x:v>
@@ -1491,8 +1539,10 @@
       <x:c r="C20" s="17" t="str">
         <x:v>通过</x:v>
       </x:c>
-      <x:c r="D20" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
+      <x:c r="D20" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
       </x:c>
       <x:c r="E20" t="str" s="15">
         <x:v>未测</x:v>
@@ -1518,8 +1568,10 @@
       <x:c r="C21" s="17" t="str">
         <x:v>通过</x:v>
       </x:c>
-      <x:c r="D21" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
+      <x:c r="D21" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
       </x:c>
       <x:c r="E21" t="str" s="15">
         <x:v>未测</x:v>
@@ -1545,8 +1597,10 @@
       <x:c r="C22" s="17" t="str">
         <x:v>通过</x:v>
       </x:c>
-      <x:c r="D22" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
+      <x:c r="D22" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
       </x:c>
       <x:c r="E22" t="str" s="15">
         <x:v>未测</x:v>
@@ -2028,6 +2082,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83b2b950b7ad4565"/>
 </x:worksheet>
 </file>
 

--- a/task_submission/4.1 内存自验证报告.xlsx
+++ b/task_submission/4.1 内存自验证报告.xlsx
@@ -772,13 +772,13 @@
     <xdr:ext cx="11430000" cy="7143750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="1f783e22-e195-4794-bef1-1ea5acf1e0bf"/>
+        <xdr:cNvPr id="1" name="51281568-0bbf-40dc-b9bd-b776aa71c49c"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R29a4323713094529"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R89a095c5444c4bae"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1039,13 +1039,13 @@
     <x:row r="1" customHeight="1">
       <x:c r="A1" s="13" t="inlineStr">
         <x:is>
-          <x:t>内存测试总结：PyTorch NPU 活跃张量分配增量，开发环境自测
-1、Ascend910_9382 / CANN 9.1.0；指定 OS/驱动待复测。
-2、计划 35，适用 10，实测通过 10，失败 0，未测 0；其余 25 不适用（任务书 3.5）。
-3、显式 workspace=0；allocated/active 峰值增量均≤输出字节+16 KiB，释放回基线。
-4、F 为 active 峰值增量/10^9，单位 GB；不是整卡 HBM；标杆未测，rato 不可计算。
-5、20 次重复回收仅 018 的两入口实测；2×64 KiB 片上 UB 不计入张量分配。
-6、shape=[B,H,L,D]；完整字节数/回收记录见“完整统计”；真实截图见D40（本次补测）。</x:t>
+          <x:t>内存测试总结：分配器活跃张量峰值增量，2026-10-30
+1、35个ID完整保留，适用10，实测10/10通过，其余25不适用。
+2、workspace=0；allocated/active增量≤输出+16KiB，释放回基线。
+3、F=active峰值增量/10^9 GB；标杆内存未测，rato不可计算。
+4、page_size:1g：大池预留1GiB，另有2MiB小池；不是workspace。
+5、UB为2×92KiB；20次重复回收仅018两入口；真实截图见D40。
+6、当前OS/driver与指定环境不同；reserved原始字段见证据JSON。</x:t>
         </x:is>
       </x:c>
       <x:c r="B1" s="3"/>
@@ -1125,20 +1125,21 @@
       <x:c r="B5" s="17" t="str">
         <x:v>float16</x:v>
       </x:c>
-      <x:c r="C5" s="17" t="str">
-        <x:v>通过</x:v>
+      <x:c r="C5" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
       </x:c>
       <x:c r="D5" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E5" t="str" s="19">
         <x:v>未测</x:v>
       </x:c>
-      <x:c r="F5" s="20" t="n">
-        <x:f>'完整统计'!AC3</x:f>
-        <x:v>0.000013824</x:v>
+      <x:c r="F5" s="20">
+        <x:v>1.3824e-05</x:v>
       </x:c>
       <x:c r="G5" t="str" s="19">
         <x:v>不可计算</x:v>
@@ -1232,19 +1233,20 @@
       <x:c r="B9" s="17" t="str">
         <x:v>float16</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str">
-        <x:v>通过</x:v>
+      <x:c r="C9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
       </x:c>
       <x:c r="D9" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" t="str" s="19">
         <x:v>未测</x:v>
       </x:c>
-      <x:c r="F9" s="20" t="n">
-        <x:f>'完整统计'!AC7</x:f>
+      <x:c r="F9" s="20">
         <x:v>0.000266752</x:v>
       </x:c>
       <x:c r="G9" t="str" s="19">
@@ -1261,19 +1263,20 @@
       <x:c r="B10" s="17" t="str">
         <x:v>float16</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str">
-        <x:v>通过</x:v>
+      <x:c r="C10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
       </x:c>
       <x:c r="D10" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" t="str" s="19">
         <x:v>未测</x:v>
       </x:c>
-      <x:c r="F10" s="20" t="n">
-        <x:f>'完整统计'!AC8</x:f>
+      <x:c r="F10" s="20">
         <x:v>0.012621312</x:v>
       </x:c>
       <x:c r="G10" t="str" s="19">
@@ -1290,19 +1293,20 @@
       <x:c r="B11" s="17" t="str">
         <x:v>float16</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str">
-        <x:v>通过</x:v>
+      <x:c r="C11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
       </x:c>
       <x:c r="D11" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" t="str" s="19">
         <x:v>未测</x:v>
       </x:c>
-      <x:c r="F11" s="20" t="n">
-        <x:f>'完整统计'!AC9</x:f>
+      <x:c r="F11" s="20">
         <x:v>0.134317568</x:v>
       </x:c>
       <x:c r="G11" t="str" s="19">
@@ -1319,19 +1323,20 @@
       <x:c r="B12" s="17" t="str">
         <x:v>float16</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str">
-        <x:v>通过</x:v>
+      <x:c r="C12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
       </x:c>
       <x:c r="D12" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" t="str" s="19">
         <x:v>未测</x:v>
       </x:c>
-      <x:c r="F12" s="20" t="n">
-        <x:f>'完整统计'!AC10</x:f>
+      <x:c r="F12" s="20">
         <x:v>0.00419584</x:v>
       </x:c>
       <x:c r="G12" t="str" s="19">
@@ -1400,20 +1405,21 @@
       <x:c r="B15" s="17" t="str">
         <x:v>bfloat16</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str">
-        <x:v>通过</x:v>
+      <x:c r="C15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
       </x:c>
       <x:c r="D15" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E15" t="str" s="15">
         <x:v>未测</x:v>
       </x:c>
-      <x:c r="F15" s="21" t="n">
-        <x:f>'完整统计'!AC13</x:f>
-        <x:v>0.000013824</x:v>
+      <x:c r="F15" s="21">
+        <x:v>1.3824e-05</x:v>
       </x:c>
       <x:c r="G15" t="str" s="15">
         <x:v>不可计算</x:v>
@@ -1507,19 +1513,20 @@
       <x:c r="B19" s="17" t="str">
         <x:v>bfloat16</x:v>
       </x:c>
-      <x:c r="C19" s="17" t="str">
-        <x:v>通过</x:v>
+      <x:c r="C19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
       </x:c>
       <x:c r="D19" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" t="str" s="15">
         <x:v>未测</x:v>
       </x:c>
-      <x:c r="F19" s="21" t="n">
-        <x:f>'完整统计'!AC17</x:f>
+      <x:c r="F19" s="21">
         <x:v>0.000266752</x:v>
       </x:c>
       <x:c r="G19" t="str" s="15">
@@ -1536,19 +1543,20 @@
       <x:c r="B20" s="17" t="str">
         <x:v>bfloat16</x:v>
       </x:c>
-      <x:c r="C20" s="17" t="str">
-        <x:v>通过</x:v>
+      <x:c r="C20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
       </x:c>
       <x:c r="D20" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E20" t="str" s="15">
         <x:v>未测</x:v>
       </x:c>
-      <x:c r="F20" s="21" t="n">
-        <x:f>'完整统计'!AC18</x:f>
+      <x:c r="F20" s="21">
         <x:v>0.012621312</x:v>
       </x:c>
       <x:c r="G20" t="str" s="15">
@@ -1565,19 +1573,20 @@
       <x:c r="B21" s="17" t="str">
         <x:v>bfloat16</x:v>
       </x:c>
-      <x:c r="C21" s="17" t="str">
-        <x:v>通过</x:v>
+      <x:c r="C21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
       </x:c>
       <x:c r="D21" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E21" t="str" s="15">
         <x:v>未测</x:v>
       </x:c>
-      <x:c r="F21" s="21" t="n">
-        <x:f>'完整统计'!AC19</x:f>
+      <x:c r="F21" s="21">
         <x:v>0.134317568</x:v>
       </x:c>
       <x:c r="G21" t="str" s="15">
@@ -1594,19 +1603,20 @@
       <x:c r="B22" s="17" t="str">
         <x:v>bfloat16</x:v>
       </x:c>
-      <x:c r="C22" s="17" t="str">
-        <x:v>通过</x:v>
+      <x:c r="C22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
       </x:c>
       <x:c r="D22" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" t="str" s="15">
         <x:v>未测</x:v>
       </x:c>
-      <x:c r="F22" s="21" t="n">
-        <x:f>'完整统计'!AC20</x:f>
+      <x:c r="F22" s="21">
         <x:v>0.00419584</x:v>
       </x:c>
       <x:c r="G22" t="str" s="15">
@@ -2082,7 +2092,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83b2b950b7ad4565"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf221a76eca104d61"/>
 </x:worksheet>
 </file>
 
@@ -2355,48 +2365,53 @@
       <x:c r="P3" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q3" s="7" t="str">
-        <x:v>通过（开发环境）</x:v>
-      </x:c>
-      <x:c r="R3" s="7" t="n">
+      <x:c r="Q3" s="7" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R3" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S3" s="7" t="n">
+      <x:c r="S3" s="7">
         <x:v>12288</x:v>
       </x:c>
-      <x:c r="T3" s="7" t="n">
+      <x:c r="T3" s="7">
         <x:v>13824</x:v>
       </x:c>
-      <x:c r="U3" s="7" t="n">
+      <x:c r="U3" s="7">
         <x:v>13824</x:v>
       </x:c>
-      <x:c r="V3" s="7" t="n">
+      <x:c r="V3" s="7">
         <x:v>28672</x:v>
       </x:c>
-      <x:c r="W3" s="7" t="n">
+      <x:c r="W3" s="7">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="X3" s="7" t="n">
+      <x:c r="X3" s="7">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="Y3" s="7" t="n">
+      <x:c r="Y3" s="7">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="Z3" s="7" t="n">
+      <x:c r="Z3" s="7">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="AA3" s="7" t="n">
+      <x:c r="AA3" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AB3" s="7" t="str">
-        <x:v>无逐case20次记录</x:v>
-      </x:c>
-      <x:c r="AC3" s="11" t="n">
-        <x:f>U3/1000000000</x:f>
-        <x:v>0.000013824</x:v>
-      </x:c>
-      <x:c r="AD3" s="7" t="str">
-        <x:v>raw/reports/final_176_01/extended.json#/records/196</x:v>
+      <x:c r="AB3" s="7" t="inlineStr">
+        <x:is>
+          <x:t>无逐case20次记录</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AC3" s="11">
+        <x:v>1.3824e-05</x:v>
+      </x:c>
+      <x:c r="AD3" s="7" t="inlineStr">
+        <x:is>
+          <x:t>raw/reports/visible_page1g_final_memory.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -2724,48 +2739,53 @@
       <x:c r="P7" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q7" s="7" t="str">
-        <x:v>通过（开发环境）</x:v>
-      </x:c>
-      <x:c r="R7" s="7" t="n">
+      <x:c r="Q7" s="7" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R7" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S7" s="7" t="n">
+      <x:c r="S7" s="7">
         <x:v>265216</x:v>
       </x:c>
-      <x:c r="T7" s="7" t="n">
+      <x:c r="T7" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="U7" s="7" t="n">
+      <x:c r="U7" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="V7" s="7" t="n">
+      <x:c r="V7" s="7">
         <x:v>281600</x:v>
       </x:c>
-      <x:c r="W7" s="7" t="n">
+      <x:c r="W7" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="X7" s="7" t="n">
+      <x:c r="X7" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="Y7" s="7" t="n">
+      <x:c r="Y7" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="Z7" s="7" t="n">
+      <x:c r="Z7" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="AA7" s="7" t="n">
+      <x:c r="AA7" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AB7" s="7" t="str">
-        <x:v>无逐case20次记录</x:v>
-      </x:c>
-      <x:c r="AC7" s="11" t="n">
-        <x:f>U7/1000000000</x:f>
+      <x:c r="AB7" s="7" t="inlineStr">
+        <x:is>
+          <x:t>无逐case20次记录</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AC7" s="11">
         <x:v>0.000266752</x:v>
       </x:c>
-      <x:c r="AD7" s="7" t="str">
-        <x:v>raw/reports/final_176_01/extended.json#/records/197</x:v>
+      <x:c r="AD7" s="7" t="inlineStr">
+        <x:is>
+          <x:t>raw/reports/visible_page1g_final_memory.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -2817,48 +2837,53 @@
       <x:c r="P8" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q8" s="7" t="str">
-        <x:v>通过（开发环境）</x:v>
-      </x:c>
-      <x:c r="R8" s="7" t="n">
+      <x:c r="Q8" s="7" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R8" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S8" s="7" t="n">
+      <x:c r="S8" s="7">
         <x:v>12619776</x:v>
       </x:c>
-      <x:c r="T8" s="7" t="n">
+      <x:c r="T8" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="U8" s="7" t="n">
+      <x:c r="U8" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="V8" s="7" t="n">
+      <x:c r="V8" s="7">
         <x:v>12636160</x:v>
       </x:c>
-      <x:c r="W8" s="7" t="n">
+      <x:c r="W8" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="X8" s="7" t="n">
+      <x:c r="X8" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="Y8" s="7" t="n">
+      <x:c r="Y8" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="Z8" s="7" t="n">
+      <x:c r="Z8" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="AA8" s="7" t="n">
+      <x:c r="AA8" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AB8" s="7" t="str">
-        <x:v>无逐case20次记录</x:v>
-      </x:c>
-      <x:c r="AC8" s="11" t="n">
-        <x:f>U8/1000000000</x:f>
+      <x:c r="AB8" s="7" t="inlineStr">
+        <x:is>
+          <x:t>无逐case20次记录</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AC8" s="11">
         <x:v>0.012621312</x:v>
       </x:c>
-      <x:c r="AD8" s="7" t="str">
-        <x:v>raw/reports/final_176_01/extended.json#/records/198</x:v>
+      <x:c r="AD8" s="7" t="inlineStr">
+        <x:is>
+          <x:t>raw/reports/visible_page1g_final_memory.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -2910,48 +2935,53 @@
       <x:c r="P9" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q9" s="7" t="str">
-        <x:v>通过（开发环境）</x:v>
-      </x:c>
-      <x:c r="R9" s="7" t="n">
+      <x:c r="Q9" s="7" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R9" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S9" s="7" t="n">
+      <x:c r="S9" s="7">
         <x:v>134316032</x:v>
       </x:c>
-      <x:c r="T9" s="7" t="n">
+      <x:c r="T9" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="U9" s="7" t="n">
+      <x:c r="U9" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="V9" s="7" t="n">
+      <x:c r="V9" s="7">
         <x:v>134332416</x:v>
       </x:c>
-      <x:c r="W9" s="7" t="n">
+      <x:c r="W9" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="X9" s="7" t="n">
+      <x:c r="X9" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="Y9" s="7" t="n">
+      <x:c r="Y9" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="Z9" s="7" t="n">
+      <x:c r="Z9" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="AA9" s="7" t="n">
+      <x:c r="AA9" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AB9" s="7" t="str">
-        <x:v>无逐case20次记录</x:v>
-      </x:c>
-      <x:c r="AC9" s="11" t="n">
-        <x:f>U9/1000000000</x:f>
+      <x:c r="AB9" s="7" t="inlineStr">
+        <x:is>
+          <x:t>无逐case20次记录</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AC9" s="11">
         <x:v>0.134317568</x:v>
       </x:c>
-      <x:c r="AD9" s="7" t="str">
-        <x:v>raw/reports/final_176_01/extended.json#/records/199</x:v>
+      <x:c r="AD9" s="7" t="inlineStr">
+        <x:is>
+          <x:t>raw/reports/visible_page1g_final_memory.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -3003,48 +3033,53 @@
       <x:c r="P10" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q10" s="7" t="str">
-        <x:v>通过（开发环境）</x:v>
-      </x:c>
-      <x:c r="R10" s="7" t="n">
+      <x:c r="Q10" s="7" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R10" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S10" s="7" t="n">
+      <x:c r="S10" s="7">
         <x:v>4195072</x:v>
       </x:c>
-      <x:c r="T10" s="7" t="n">
+      <x:c r="T10" s="7">
         <x:v>4195840</x:v>
       </x:c>
-      <x:c r="U10" s="7" t="n">
+      <x:c r="U10" s="7">
         <x:v>4195840</x:v>
       </x:c>
-      <x:c r="V10" s="7" t="n">
+      <x:c r="V10" s="7">
         <x:v>4211456</x:v>
       </x:c>
-      <x:c r="W10" s="7" t="n">
+      <x:c r="W10" s="7">
         <x:v>4196352</x:v>
       </x:c>
-      <x:c r="X10" s="7" t="n">
+      <x:c r="X10" s="7">
         <x:v>4196352</x:v>
       </x:c>
-      <x:c r="Y10" s="7" t="n">
+      <x:c r="Y10" s="7">
         <x:v>4196352</x:v>
       </x:c>
-      <x:c r="Z10" s="7" t="n">
+      <x:c r="Z10" s="7">
         <x:v>4196352</x:v>
       </x:c>
-      <x:c r="AA10" s="7" t="n">
+      <x:c r="AA10" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AB10" s="7" t="str">
-        <x:v>无逐case20次记录</x:v>
-      </x:c>
-      <x:c r="AC10" s="11" t="n">
-        <x:f>U10/1000000000</x:f>
+      <x:c r="AB10" s="7" t="inlineStr">
+        <x:is>
+          <x:t>无逐case20次记录</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AC10" s="11">
         <x:v>0.00419584</x:v>
       </x:c>
-      <x:c r="AD10" s="7" t="str">
-        <x:v>raw/reports/final_176_01/extended.json#/records/200</x:v>
+      <x:c r="AD10" s="7" t="inlineStr">
+        <x:is>
+          <x:t>raw/reports/visible_page1g_final_memory.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -3280,48 +3315,53 @@
       <x:c r="P13" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q13" s="7" t="str">
-        <x:v>通过（开发环境）</x:v>
-      </x:c>
-      <x:c r="R13" s="7" t="n">
+      <x:c r="Q13" s="7" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R13" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S13" s="7" t="n">
+      <x:c r="S13" s="7">
         <x:v>12288</x:v>
       </x:c>
-      <x:c r="T13" s="7" t="n">
+      <x:c r="T13" s="7">
         <x:v>13824</x:v>
       </x:c>
-      <x:c r="U13" s="7" t="n">
+      <x:c r="U13" s="7">
         <x:v>13824</x:v>
       </x:c>
-      <x:c r="V13" s="7" t="n">
+      <x:c r="V13" s="7">
         <x:v>28672</x:v>
       </x:c>
-      <x:c r="W13" s="7" t="n">
+      <x:c r="W13" s="7">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="X13" s="7" t="n">
+      <x:c r="X13" s="7">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="Y13" s="7" t="n">
+      <x:c r="Y13" s="7">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="Z13" s="7" t="n">
+      <x:c r="Z13" s="7">
         <x:v>12800</x:v>
       </x:c>
-      <x:c r="AA13" s="7" t="n">
+      <x:c r="AA13" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AB13" s="7" t="str">
-        <x:v>无逐case20次记录</x:v>
-      </x:c>
-      <x:c r="AC13" s="11" t="n">
-        <x:f>U13/1000000000</x:f>
-        <x:v>0.000013824</x:v>
-      </x:c>
-      <x:c r="AD13" s="7" t="str">
-        <x:v>raw/reports/final_176_01/extended.json#/records/201</x:v>
+      <x:c r="AB13" s="7" t="inlineStr">
+        <x:is>
+          <x:t>无逐case20次记录</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AC13" s="11">
+        <x:v>1.3824e-05</x:v>
+      </x:c>
+      <x:c r="AD13" s="7" t="inlineStr">
+        <x:is>
+          <x:t>raw/reports/visible_page1g_final_memory.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
@@ -3649,48 +3689,53 @@
       <x:c r="P17" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q17" s="7" t="str">
-        <x:v>通过（开发环境）</x:v>
-      </x:c>
-      <x:c r="R17" s="7" t="n">
+      <x:c r="Q17" s="7" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R17" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S17" s="7" t="n">
+      <x:c r="S17" s="7">
         <x:v>265216</x:v>
       </x:c>
-      <x:c r="T17" s="7" t="n">
+      <x:c r="T17" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="U17" s="7" t="n">
+      <x:c r="U17" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="V17" s="7" t="n">
+      <x:c r="V17" s="7">
         <x:v>281600</x:v>
       </x:c>
-      <x:c r="W17" s="7" t="n">
+      <x:c r="W17" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="X17" s="7" t="n">
+      <x:c r="X17" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="Y17" s="7" t="n">
+      <x:c r="Y17" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="Z17" s="7" t="n">
+      <x:c r="Z17" s="7">
         <x:v>266752</x:v>
       </x:c>
-      <x:c r="AA17" s="7" t="n">
+      <x:c r="AA17" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AB17" s="7" t="str">
-        <x:v>无逐case20次记录</x:v>
-      </x:c>
-      <x:c r="AC17" s="11" t="n">
-        <x:f>U17/1000000000</x:f>
+      <x:c r="AB17" s="7" t="inlineStr">
+        <x:is>
+          <x:t>无逐case20次记录</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AC17" s="11">
         <x:v>0.000266752</x:v>
       </x:c>
-      <x:c r="AD17" s="7" t="str">
-        <x:v>raw/reports/final_176_01/extended.json#/records/202</x:v>
+      <x:c r="AD17" s="7" t="inlineStr">
+        <x:is>
+          <x:t>raw/reports/visible_page1g_final_memory.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
@@ -3742,48 +3787,53 @@
       <x:c r="P18" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q18" s="7" t="str">
-        <x:v>通过（开发环境）</x:v>
-      </x:c>
-      <x:c r="R18" s="7" t="n">
+      <x:c r="Q18" s="7" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R18" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S18" s="7" t="n">
+      <x:c r="S18" s="7">
         <x:v>12619776</x:v>
       </x:c>
-      <x:c r="T18" s="7" t="n">
+      <x:c r="T18" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="U18" s="7" t="n">
+      <x:c r="U18" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="V18" s="7" t="n">
+      <x:c r="V18" s="7">
         <x:v>12636160</x:v>
       </x:c>
-      <x:c r="W18" s="7" t="n">
+      <x:c r="W18" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="X18" s="7" t="n">
+      <x:c r="X18" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="Y18" s="7" t="n">
+      <x:c r="Y18" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="Z18" s="7" t="n">
+      <x:c r="Z18" s="7">
         <x:v>12621312</x:v>
       </x:c>
-      <x:c r="AA18" s="7" t="n">
+      <x:c r="AA18" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AB18" s="7" t="str">
-        <x:v>无逐case20次记录</x:v>
-      </x:c>
-      <x:c r="AC18" s="11" t="n">
-        <x:f>U18/1000000000</x:f>
+      <x:c r="AB18" s="7" t="inlineStr">
+        <x:is>
+          <x:t>无逐case20次记录</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AC18" s="11">
         <x:v>0.012621312</x:v>
       </x:c>
-      <x:c r="AD18" s="7" t="str">
-        <x:v>raw/reports/final_176_01/extended.json#/records/203</x:v>
+      <x:c r="AD18" s="7" t="inlineStr">
+        <x:is>
+          <x:t>raw/reports/visible_page1g_final_memory.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
@@ -3835,48 +3885,53 @@
       <x:c r="P19" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q19" s="7" t="str">
-        <x:v>通过（开发环境）</x:v>
-      </x:c>
-      <x:c r="R19" s="7" t="n">
+      <x:c r="Q19" s="7" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R19" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S19" s="7" t="n">
+      <x:c r="S19" s="7">
         <x:v>134316032</x:v>
       </x:c>
-      <x:c r="T19" s="7" t="n">
+      <x:c r="T19" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="U19" s="7" t="n">
+      <x:c r="U19" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="V19" s="7" t="n">
+      <x:c r="V19" s="7">
         <x:v>134332416</x:v>
       </x:c>
-      <x:c r="W19" s="7" t="n">
+      <x:c r="W19" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="X19" s="7" t="n">
+      <x:c r="X19" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="Y19" s="7" t="n">
+      <x:c r="Y19" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="Z19" s="7" t="n">
+      <x:c r="Z19" s="7">
         <x:v>134317568</x:v>
       </x:c>
-      <x:c r="AA19" s="7" t="n">
+      <x:c r="AA19" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AB19" s="7" t="str">
-        <x:v>无逐case20次记录</x:v>
-      </x:c>
-      <x:c r="AC19" s="11" t="n">
-        <x:f>U19/1000000000</x:f>
+      <x:c r="AB19" s="7" t="inlineStr">
+        <x:is>
+          <x:t>无逐case20次记录</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AC19" s="11">
         <x:v>0.134317568</x:v>
       </x:c>
-      <x:c r="AD19" s="7" t="str">
-        <x:v>raw/reports/final_176_01/extended.json#/records/204</x:v>
+      <x:c r="AD19" s="7" t="inlineStr">
+        <x:is>
+          <x:t>raw/reports/visible_page1g_final_memory.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
@@ -3928,48 +3983,53 @@
       <x:c r="P20" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q20" s="7" t="str">
-        <x:v>通过（开发环境）</x:v>
-      </x:c>
-      <x:c r="R20" s="7" t="n">
+      <x:c r="Q20" s="7" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R20" s="7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S20" s="7" t="n">
+      <x:c r="S20" s="7">
         <x:v>4195072</x:v>
       </x:c>
-      <x:c r="T20" s="7" t="n">
+      <x:c r="T20" s="7">
         <x:v>4195840</x:v>
       </x:c>
-      <x:c r="U20" s="7" t="n">
+      <x:c r="U20" s="7">
         <x:v>4195840</x:v>
       </x:c>
-      <x:c r="V20" s="7" t="n">
+      <x:c r="V20" s="7">
         <x:v>4211456</x:v>
       </x:c>
-      <x:c r="W20" s="7" t="n">
+      <x:c r="W20" s="7">
         <x:v>4196352</x:v>
       </x:c>
-      <x:c r="X20" s="7" t="n">
+      <x:c r="X20" s="7">
         <x:v>4196352</x:v>
       </x:c>
-      <x:c r="Y20" s="7" t="n">
+      <x:c r="Y20" s="7">
         <x:v>4196352</x:v>
       </x:c>
-      <x:c r="Z20" s="7" t="n">
+      <x:c r="Z20" s="7">
         <x:v>4196352</x:v>
       </x:c>
-      <x:c r="AA20" s="7" t="n">
+      <x:c r="AA20" s="7">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AB20" s="7" t="str">
-        <x:v>018两入口通过</x:v>
-      </x:c>
-      <x:c r="AC20" s="11" t="n">
-        <x:f>U20/1000000000</x:f>
+      <x:c r="AB20" s="7" t="inlineStr">
+        <x:is>
+          <x:t>两入口各20次通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AC20" s="11">
         <x:v>0.00419584</x:v>
       </x:c>
-      <x:c r="AD20" s="7" t="str">
-        <x:v>raw/reports/final_176_01/extended.json#/records/205</x:v>
+      <x:c r="AD20" s="7" t="inlineStr">
+        <x:is>
+          <x:t>raw/reports/visible_page1g_final_memory.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
